--- a/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensual'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="12">
@@ -174,69 +182,80 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="10" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="11" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -596,15 +615,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -612,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -640,9 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -664,8 +683,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -674,18 +710,18 @@
   <sheetPr>
     <tabColor rgb="00EFEBE9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -860,6 +897,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -980,6 +1018,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1138,6 +1177,7 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
@@ -1257,6 +1297,26 @@
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>COUNTIF(E6:E34,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>COUNTIF(B6:B34,"?*")</f>
+        <v>23.0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -1283,12 +1343,26 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E31 E32 E33 E34" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1297,18 +1371,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1325,6 +1399,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1464,6 +1539,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1603,6 +1679,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1723,6 +1800,26 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>COUNTIF(E6:E25,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>COUNTIF(B6:B25,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
@@ -1740,18 +1837,32 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A27:G27"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Semanal'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensual'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Trimestral y Anual'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -90,7 +92,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -157,6 +159,11 @@
         <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -184,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,6 +248,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -617,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -685,9 +695,38 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Más allá del mes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge lo que se CONTRATA y se pide por escrito en una inspección: DDD, conductos de extracción, analíticas, carnés de manipulador, SAT de temperadora y cámaras, calibración de sondas y báscula, extintores, instalación de gas, RGSEAA, póliza y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Anota en «Notas» el número de parte de cada revisión y la fecha de la siguiente; la columna «Cadencia» ya viene con la periodicidad legal o recomendada de cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1286,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperaturas de cámaras frigoríficas</t>
+          <t>Verificar y registrar las temperaturas de los equipos de frío: cámara de conservación 15-18 °C y nevera de rellenos 0-4 °C — anota las lecturas: ____ °C / ____ °C</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -1305,8 +1344,8 @@
         </is>
       </c>
       <c r="C35">
-        <f>COUNTIF(E6:E34,"✓")</f>
-        <v>3.0</v>
+        <f>COUNTIFS(B6:B34,"?*",E6:E34,"✓")-COUNTIFS(B6:B34,"Tarea",E6:E34,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1314,8 +1353,8 @@
         </is>
       </c>
       <c r="E35">
-        <f>COUNTIF(B6:B34,"?*")</f>
-        <v>23.0</v>
+        <f>COUNTIF(B6:B34,"?*")-COUNTIF(B6:B34,"Tarea")-COUNTIF(E6:E34,"N/A")</f>
+        <v>20.0</v>
       </c>
     </row>
     <row r="36">
@@ -1349,8 +1388,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E22 E23 E24 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1730,7 +1769,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Revisar registros APPCC del mes: temperaturas, limpieza</t>
+          <t>Revisar registros APPCC del mes: temperaturas, limpieza (si tienes el Pack APPCC, regístralo allí; si no, anótalo junto a la tarea)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -1807,8 +1846,8 @@
         </is>
       </c>
       <c r="C26">
-        <f>COUNTIF(E6:E25,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B25,"?*",E6:E25,"✓")-COUNTIFS(B6:B25,"Tarea",E6:E25,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1816,8 +1855,8 @@
         </is>
       </c>
       <c r="E26">
-        <f>COUNTIF(B6:B25,"?*")</f>
-        <v>16.0</v>
+        <f>COUNTIF(B6:B25,"?*")-COUNTIF(B6:B25,"Tarea")-COUNTIF(E6:E25,"N/A")</f>
+        <v>14.0</v>
       </c>
     </row>
     <row r="27">
@@ -1850,8 +1889,565 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF8E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit de Tareas: Chocolatería / Obrador de Chocolate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Higiene, plagas y analíticas — empresa autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD) por empresa autorizada: visita, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza de los conductos de extracción del obrador por empresa homologada, con certificado</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Analítica de superficies, de producto y del agua de la red interior en laboratorio externo (legionela sólo si tienes torre de refrigeración o acumulador de agua caliente)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Renovar los carnés de manipulador de alimentos del equipo y archivar los certificados</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Revisar el plan de autocontrol de higiene y las fichas técnicas de producto: altas, bajas y cambios de proveedor del año</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Equipos, instalaciones y seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la temperadora y del bombo por el SAT: sondas, resistencias, juntas y desgaste del tornillo</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Templado</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de cámaras y neveras por frigorista: gas, estanqueidad, juntas y ciclo de desescarche</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Conservación</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Calibrar termómetros, sondas y báscula de precisión contra un patrón conocido y anotar la desviación</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación de gas por empresa habilitada, si el obrador la tiene</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Documentación, seguros y facturación</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Revisar la póliza de responsabilidad civil y de continuidad de negocio: sumas aseguradas y actividades excluidas</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que el registro sanitario (RGSEAA) recoge la actividad y las instalaciones reales, obrador incluido</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del trimestre y anotar en «Notas» el nº de parte de cada revisión y la fecha de la siguiente</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(B6:B25,"?*",E6:E25,"✓")-COUNTIFS(B6:B25,"Tarea",E6:E25,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>COUNTIF(B6:B25,"?*")-COUNTIF(B6:B25,"Tarea")-COUNTIF(E6:E25,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A27:G27"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A6:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/05-tareas-semanales-mensuales.xlsx
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
